--- a/data/trans_orig/LAWTONBRODY-Clase-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONBRODY-Clase-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 7,71</t>
+          <t>6,83; 7,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,38; 7,79</t>
+          <t>6,24; 7,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,15; 7,83</t>
+          <t>7,1; 7,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,11; 7,28</t>
+          <t>6,13; 7,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,64; 7,95</t>
+          <t>5,56; 7,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,74; 7,66</t>
+          <t>5,77; 7,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,79; 7,48</t>
+          <t>6,77; 7,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,6; 7,71</t>
+          <t>6,59; 7,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,85; 7,67</t>
+          <t>6,91; 7,67</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,62; 7,63</t>
+          <t>6,76; 7,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,93; 7,64</t>
+          <t>5,93; 7,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 7,61</t>
+          <t>6,71; 7,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 7,72</t>
+          <t>5,75; 7,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,69; 7,18</t>
+          <t>4,42; 7,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,93; 7,48</t>
+          <t>4,81; 7,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,76; 7,58</t>
+          <t>6,73; 7,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,01; 7,36</t>
+          <t>5,9; 7,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,53; 7,45</t>
+          <t>6,56; 7,47</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,36; 7,35</t>
+          <t>6,42; 7,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,36; 7,36</t>
+          <t>6,43; 7,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,06; 7,64</t>
+          <t>7,02; 7,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 7,4</t>
+          <t>5,37; 7,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,77; 7,09</t>
+          <t>5,8; 7,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,86; 7,3</t>
+          <t>5,8; 7,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,42; 7,3</t>
+          <t>6,31; 7,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,47; 7,25</t>
+          <t>6,44; 7,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,84; 7,45</t>
+          <t>6,86; 7,48</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,75; 7,24</t>
+          <t>6,78; 7,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,05; 6,8</t>
+          <t>6,08; 6,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,86; 7,38</t>
+          <t>6,84; 7,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,54; 7,39</t>
+          <t>6,49; 7,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,53; 6,87</t>
+          <t>5,56; 6,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,93; 7,15</t>
+          <t>5,98; 7,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 7,23</t>
+          <t>6,82; 7,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 6,74</t>
+          <t>6,1; 6,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,73; 7,26</t>
+          <t>6,72; 7,21</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1117,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,39; 7,42</t>
+          <t>6,33; 7,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,11; 7,03</t>
+          <t>6,11; 7,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,22; 6,97</t>
+          <t>6,27; 6,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,71; 6,78</t>
+          <t>5,73; 6,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,21; 6,14</t>
+          <t>5,2; 6,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,07; 6,94</t>
+          <t>6,08; 6,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,08; 6,91</t>
+          <t>6,17; 6,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,65; 6,36</t>
+          <t>5,64; 6,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,3; 6,89</t>
+          <t>6,29; 6,84</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1242,32 +1242,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,58; 7,02</t>
+          <t>6,59; 7,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,07; 6,64</t>
+          <t>6,1; 6,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,27; 6,79</t>
+          <t>6,28; 6,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,58; 7,03</t>
+          <t>6,6; 7,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,08; 6,62</t>
+          <t>6,12; 6,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,27; 6,79</t>
+          <t>6,28; 6,81</t>
         </is>
       </c>
     </row>
@@ -1342,42 +1342,42 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,5; 6,96</t>
+          <t>6,5; 6,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,28</t>
+          <t>6,99; 7,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,58; 6,93</t>
+          <t>6,58; 6,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,03; 6,44</t>
+          <t>6,05; 6,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,41; 6,78</t>
+          <t>6,43; 6,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,77; 7,03</t>
+          <t>6,78; 7,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,3; 6,6</t>
+          <t>6,28; 6,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,69; 6,95</t>
+          <t>6,69; 6,96</t>
         </is>
       </c>
     </row>
